--- a/AAII_Financials/Quarterly/DASTY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DASTY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="92">
   <si>
     <t>DASTY</t>
   </si>
@@ -656,172 +656,176 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -858,86 +862,89 @@
       <c r="N8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="3">
         <v>3275000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1483800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2947100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1441200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2738900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1247800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2469100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1240900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2243100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1068600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2403600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1237900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2449100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1120600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1147000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2165900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>891100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1807700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>898900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1864500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>843100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1757300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>891900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1890100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -974,86 +981,89 @@
       <c r="N9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="3">
         <v>530400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>250800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>479200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>229400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>432800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>207100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>413800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>206900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>367900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>192000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>415300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>214300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>394000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>175800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>348300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>174400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>320100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>139800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>263700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>132100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>262400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>124200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>269400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>144600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>273000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>130900</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1090,86 +1100,89 @@
       <c r="N10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="3">
         <v>2744500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1233000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2467900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1211800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2306100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1040700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2055300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1034000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1875100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>876600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1988300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1023600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2055100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>944800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1910700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>972600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1845800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>751300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1544000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>766800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1602200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>718900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1487800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>747200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1617100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>732100</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1210,8 +1223,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1248,86 +1262,89 @@
       <c r="N12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="3">
         <v>630100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>310400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>564000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>266000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>523500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>251800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>493500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>250700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>460600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>238800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>516700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>251100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>444400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>208900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>393000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>215700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>375100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>170300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>344800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>167700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>303700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>157800</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>343200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>175700</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>318500</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>154700</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1442,8 +1459,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1480,86 +1500,89 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3">
         <v>14700</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3">
         <v>1200</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="3">
         <v>7900</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V14" s="3">
         <v>25500</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X14" s="3">
         <v>23900</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="3">
         <v>34800</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="3">
         <v>11700</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="3">
         <v>28200</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3">
         <v>37300</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="3">
         <v>7600</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>21700</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL14" s="3">
         <v>11900</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM14" s="3">
+      <c r="AM14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN14" s="3">
         <v>31800</v>
       </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1596,86 +1619,89 @@
       <c r="N15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="3">
         <v>228600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>112300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>212700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>104300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>206200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>102500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>189200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>94700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>184100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>96300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>229000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>119300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>166900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>62600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>118800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>59900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>105400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>48500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>90600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>45900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>89500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>43900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>90300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>48400</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>92100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>44400</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1713,8 +1739,9 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1751,86 +1778,89 @@
       <c r="N17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P17" s="3">
         <v>2547800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1197700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2243800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1076600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2137000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>992600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1977900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>997000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1836100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>939200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2118100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1073100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1964800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>885100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1791000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>888900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1668100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>722800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1426300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>702700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1370800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>663700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1433100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>751600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1434500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>674100</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1867,86 +1897,89 @@
       <c r="N18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18" s="3">
         <v>727100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>286100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>703300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>364600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>601900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>255200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>491100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>244000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>406900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>129400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>285500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>164700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>484400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>235600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>468100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>258100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>497800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>168200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>381400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>196200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>493800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>179400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>324200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>140300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>455600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>188900</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1987,8 +2020,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2025,86 +2059,89 @@
       <c r="N20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P20" s="3">
         <v>28900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>7200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>7200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>12700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>20500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>6200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>15300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>19900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>5300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>10100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>29000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>8500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>14900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2141,86 +2178,89 @@
       <c r="N21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="3">
         <v>1105900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>453000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1027100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>517000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>924000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>387400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>800700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>386900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>709900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>268500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>628600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>334000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>760000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>343900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>689500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>364800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>657900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>238700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>527800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>264700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>627500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>239100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>473700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>213300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>591700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>246600</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2257,86 +2297,89 @@
       <c r="N22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="3">
         <v>15200</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R22" s="3">
         <v>13400</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T22" s="3">
         <v>14900</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V22" s="3">
         <v>15300</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X22" s="3">
         <v>17600</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z22" s="3">
         <v>21400</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB22" s="3">
         <v>15400</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD22" s="3">
         <v>14100</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AE22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF22" s="3">
         <v>7700</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AG22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH22" s="3">
         <v>9800</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI22" s="3">
+      <c r="AI22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL22" s="3">
         <v>3700</v>
       </c>
-      <c r="AL22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM22" s="3">
+      <c r="AM22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN22" s="3">
         <v>7500</v>
       </c>
-      <c r="AN22" s="3" t="s">
+      <c r="AO22" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2373,86 +2416,89 @@
       <c r="N23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P23" s="3">
         <v>740900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>288700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>692800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>359300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>594200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>250200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>482700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>241000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>396600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>123300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>271300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>157600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>481700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>237300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>474400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>264400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>505300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>172000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>391500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>201500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>493700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>177600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>349400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>148700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>463000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>187900</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2489,86 +2535,89 @@
       <c r="N24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P24" s="3">
         <v>139900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>57300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>271000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>72000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>141700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>56300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>105500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>56800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>101100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>28700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>64800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>38500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>111600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>69600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>134100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>75200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>152500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>50000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>100500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>52200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>144900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>58500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>114600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>47300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>159400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>52900</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2683,8 +2732,11 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2721,86 +2773,89 @@
       <c r="N26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="3">
         <v>601000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>231400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>421700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>287300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>452500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>193800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>377200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>184200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>295400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>94600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>206500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>119100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>370100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>167700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>340300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>189100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>352900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>122100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>291100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>149300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>348800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>119200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>234800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>101400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>303600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>135000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2837,86 +2892,89 @@
       <c r="N27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P27" s="3">
         <v>601600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>231800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>422500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>287600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>451600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>193300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>377800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>184500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>294800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>95400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>213200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>122600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>374000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>168300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>346900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>192300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>359500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>125000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>291500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>149700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>349400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>119500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>233300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>99800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>300500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>132800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3031,8 +3089,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3069,8 +3130,8 @@
       <c r="N29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -3147,8 +3208,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3263,8 +3327,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3379,8 +3446,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3417,86 +3487,89 @@
       <c r="N32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P32" s="3">
         <v>-28900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-7200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-20500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-6200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-15300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-10100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-29000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-14900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3533,86 +3606,89 @@
       <c r="N33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P33" s="3">
         <v>601600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>231800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>422500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>287600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>451600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>193300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>377800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>184500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>294800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>95400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>213200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>122600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>374000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>168300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>346900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>192300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>359500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>125000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>291500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>149700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>349400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>119500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>233300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>99800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>300500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>132800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3727,8 +3803,11 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3765,207 +3844,213 @@
       <c r="N35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="3">
         <v>601600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>231800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>422500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>287600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>451600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>193300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>377800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>184500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>294800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>95400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>213200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>122600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>374000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>168300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>346900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>192300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>359500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>125000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>291500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>149700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>349400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>119500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>233300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>99800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>300500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>132800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4006,8 +4091,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4048,124 +4134,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6466500</v>
+      </c>
+      <c r="E41" s="3">
         <v>4843700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4795900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4585900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4092100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4319600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4418900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3944200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3652200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3564900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3652200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3768000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3066900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3012500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3435100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3273100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3230100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2875800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3088300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2871500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2143300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2601100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2617900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2447500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2270500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7173100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3638400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3464200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3323100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3041200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3341400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3078600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2759500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3076400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3107000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3246100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2860200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2879200</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4238,14 +4328,14 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB42" s="3">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC42" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC42" s="3">
-        <v>700</v>
       </c>
       <c r="AD42" s="3">
         <v>700</v>
@@ -4254,150 +4344,156 @@
         <v>700</v>
       </c>
       <c r="AF42" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG42" s="3">
         <v>600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>45300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>52200</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>54000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>74700</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>65800</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2208800</v>
+      </c>
+      <c r="E43" s="3">
         <v>2762700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2029500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1884800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2398200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1642600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1724300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2135300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1593700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1430500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1593700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1427000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1984400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1300900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1520300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1386700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1625700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1073600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1220000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1224600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1405100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>967100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1143300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1245500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1706200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>960300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1075800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1108600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1427600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>725000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>916800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>823200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1088800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>616000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>821000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>828200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1090100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>633300</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4434,8 +4530,8 @@
       <c r="N44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4512,267 +4608,276 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>358600</v>
+      </c>
+      <c r="E45" s="3">
         <v>170400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>345400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>502400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>135100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>523000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>502300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>147700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>309500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>551900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>309500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>430500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>314200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>559800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>282500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>413300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>260100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>358900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>254100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>339500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>202100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>305900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>271700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>368000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>306600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>520100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>192800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>320600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>218800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>294600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>166500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>236200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>188900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>312900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>160200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>315400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>174900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>270300</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9033900</v>
+      </c>
+      <c r="E46" s="3">
         <v>7967000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7170800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6973100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6799500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6485200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6645600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6389000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5555300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5547200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5555300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5625500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5365500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4873200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5237900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5073000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5115900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4308200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4562400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4435700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3750500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3874100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4032900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4060900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4283200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8654400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4907700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4894100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4970300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4061500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4425300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4183300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4038600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4057500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4142300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4464400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4191000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3840900</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="3">
         <v>114900</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="3">
         <v>25200</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K47" s="3">
         <v>54800</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>10</v>
       </c>
@@ -4782,8 +4887,8 @@
       <c r="N47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4821,279 +4926,288 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD47" s="3">
         <v>214800</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF47" s="3">
         <v>198100</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH47" s="3">
         <v>183500</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI47" s="3">
+      <c r="AI47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>182100</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL47" s="3">
         <v>176200</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM47" s="3">
+      <c r="AM47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN47" s="3">
         <v>205200</v>
       </c>
-      <c r="AN47" s="3" t="s">
+      <c r="AO47" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1087700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1109300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1061100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1003800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>979200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1021600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>983000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>975800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>930700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>905800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>930700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>880800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>908100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>918600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>885400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>886100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>885700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>886800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>881900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>906100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>858900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>920000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1003900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1036000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1050300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>696800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>662400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>688200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>210800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>187800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>185700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>180500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>189600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>172600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>175800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>161200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>158900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>153300</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7868300</v>
+      </c>
+      <c r="E49" s="3">
         <v>8064800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8256400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8211800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7958500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8229000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8305600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8452600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8673900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8530200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8673900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8727500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9163700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9759000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9397500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8959300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8862400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8706300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8453400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8644400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7916700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8653100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9569200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9808800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10409800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4502200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4251300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4411000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3859000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3671300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3319900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3183300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3354900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3021700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3108600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3373200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3435200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3371400</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5208,8 +5322,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5324,124 +5441,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>372000</v>
+      </c>
+      <c r="E52" s="3">
         <v>132600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>254800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>387900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>129800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>281500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>296600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>145000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>256100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>317100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>256100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>357600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>358200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>340300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>321900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>578800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>550500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>496900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>468300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>453900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>404400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>430600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>456200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>429500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>451700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>420400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>226100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>421900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>194200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>341900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>128600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>300100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>122200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>323600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>145200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>366800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>159500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>375600</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5556,124 +5679,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18642400</v>
+      </c>
+      <c r="E54" s="3">
         <v>17681600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16929300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16576600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16094700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16017300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16230800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16162800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15535300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15300300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15535300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15591400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15795600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15891200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15842600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15497300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15414500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14398300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14366100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14440000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12930500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13877800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15062200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15335200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16195000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>14273800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10262300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10415200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9432400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8262500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8242900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7847200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7887400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7575300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>7748100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>8365500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>8149800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>7741300</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5714,8 +5843,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5756,217 +5886,221 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>276200</v>
+      </c>
+      <c r="E57" s="3">
         <v>297100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>215100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>215600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>269100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>213100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>211600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>254800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>193600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>217900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>193600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>196800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>239600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>226000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>199700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>182500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>208600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>152500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>140500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>146000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>171300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>150100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>161800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>181300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>256800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>196100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>192700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>162600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>191300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>154300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>145700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>141500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>167500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>141300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>154000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>149200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>170000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>144100</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1413800</v>
+      </c>
+      <c r="E58" s="3">
         <v>1797000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>627100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>444700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>558100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1021300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1026500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1123700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>277700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1005700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>277700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>294200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>284500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>274200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>980500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>985800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>977200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>971800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>347600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>10500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>13700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>13800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>14100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>411700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>418700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>414000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>387700</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>10</v>
       </c>
@@ -5979,8 +6113,8 @@
       <c r="AK58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AL58" s="3">
-        <v>0</v>
+      <c r="AL58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AM58" s="3">
         <v>0</v>
@@ -5988,338 +6122,347 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2288500</v>
+      </c>
+      <c r="E59" s="3">
         <v>2006700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2410900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3054200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2029900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2582400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2618600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1701200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1911900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2287400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1911900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2607500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2666900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2326700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2447100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2455200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2576400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1977600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2141300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2165200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1896600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1764800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2075900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2078600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2229100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1850700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1933300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1908300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1787500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1360900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1528000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1459200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1546300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1361100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1604000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1758700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1550300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1454700</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4542900</v>
+      </c>
+      <c r="E60" s="3">
         <v>4965700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3921900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3714400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3645800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3816900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3856700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3936100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2952200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3511000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2952200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3098400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3191000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2826900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3627300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3623500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3762200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3101900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2629300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2321700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2081500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1928700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2239600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2267600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2491000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2060900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2537700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2489500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2392800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1902900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1673700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1600800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1713800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1502300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1758100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1907900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1720400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1598800</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2445100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1924200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2400400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2208500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2612200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2188400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2202300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2856500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2990000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2159100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2990000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2974900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3031900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2963100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2978000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2976200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3215900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3190500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4082400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4429300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4163400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4754000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5018300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5028800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5366400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4444900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>764700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>777500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>768900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>719900</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>1098000</v>
       </c>
       <c r="AH61" s="3">
         <v>1098000</v>
       </c>
       <c r="AI61" s="3">
-        <v>1122000</v>
+        <v>1098000</v>
       </c>
       <c r="AJ61" s="3">
         <v>1122000</v>
@@ -6328,7 +6471,7 @@
         <v>1122000</v>
       </c>
       <c r="AL61" s="3">
-        <v>1173800</v>
+        <v>1122000</v>
       </c>
       <c r="AM61" s="3">
         <v>1173800</v>
@@ -6336,124 +6479,130 @@
       <c r="AN61" s="3">
         <v>1173800</v>
       </c>
+      <c r="AO61" s="3">
+        <v>1173800</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E62" s="3">
         <v>247200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>943000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>959800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>247900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1281700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1275100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>428400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1127700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1400400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1127700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1390800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1459700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1644400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1609300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1735700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1703100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1684700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1680200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1745500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1592700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1792500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1952700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2074900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2194000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1342200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1248000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1298400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>798800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>688300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>549400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>548300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>568100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>619100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>612100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>682500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>697900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>677600</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6568,8 +6717,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6684,8 +6836,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6800,124 +6955,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7991000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7351800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7304200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6882700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6693400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7286900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7334100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7490300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7355900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7070500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7355900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7464100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7698400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7450200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8230500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8351200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8696000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7986200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8440800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8545800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7882400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8522300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9263200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9428100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10114300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7919300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4618200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4639100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4036100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3375700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3322800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3248900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3405900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3245800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3494900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3764200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>3618700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>3474700</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6958,8 +7119,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7074,8 +7236,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7190,8 +7355,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7306,8 +7474,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7422,124 +7593,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>9821700</v>
+      </c>
+      <c r="E72" s="3">
         <v>9953400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9282800</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H72" s="3">
         <v>8296700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7797500</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K72" s="3">
         <v>7925400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7094300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N72" s="3">
         <v>7094300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P72" s="3">
         <v>6986500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R72" s="3">
         <v>6231900</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T72" s="3">
         <v>6193000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="V72" s="3">
         <v>5472700</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X72" s="3">
         <v>5030600</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z72" s="3">
         <v>5074900</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB72" s="3">
         <v>5432200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD72" s="3">
         <v>4866100</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF72" s="3">
         <v>4735700</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH72" s="3">
         <v>4099400</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>4015600</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL72" s="3">
         <v>3643500</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AM72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN72" s="3">
         <v>3725200</v>
       </c>
-      <c r="AN72" s="3" t="s">
+      <c r="AO72" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7654,8 +7831,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7770,8 +7950,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7886,124 +8069,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10645300</v>
+      </c>
+      <c r="E76" s="3">
         <v>10323500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9611600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9678400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9386700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8716900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8882900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8659300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8166600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8217500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8166600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8114200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8097200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8440900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7612100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7146100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6718500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6412100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5925200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5894200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5048100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5355500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5799000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5907200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6080800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6354500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5644100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5776100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5396400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4886700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4920100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4598300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4481400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4329500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4253200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4601300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4531200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4266600</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8118,129 +8307,135 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8277,86 +8472,89 @@
       <c r="N81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P81" s="3">
         <v>601600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>231800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>422500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>287600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>451600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>193300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>377800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>184500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>294800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>95400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>213200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>122600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>374000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>168300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>346900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>192300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>359500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>125000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>291500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>149700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>349400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>119500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>233300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>99800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>300500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>132800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8397,124 +8595,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-107200</v>
+      </c>
+      <c r="E83" s="3">
         <v>48300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>51400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-169800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>50500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>48700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-141200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>49600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>51000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>49600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>51000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>349900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>164400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>320900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>157700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>314900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>137200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>302700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>145900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>295800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>145200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>335900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>176400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>262900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>106600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>200900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>100500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>144900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>66700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>126500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>63200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>123700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>61500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>120600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>64600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>121200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>58600</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8629,8 +8831,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8745,8 +8950,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8861,8 +9069,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8977,8 +9188,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9093,124 +9307,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>329400</v>
+      </c>
+      <c r="E89" s="3">
         <v>347900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>392600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>878700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>323000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>492100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>723800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>324400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>265100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>260400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>265100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>850700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>528700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>251500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1140200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>685900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>628600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>232600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1093200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>679000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>385200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>153800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>932800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>499700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>341400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>134900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1051200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>584300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>299400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>112000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>708800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>446800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>171300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>89100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>664700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>408300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>202700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9251,124 +9471,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-43600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-46300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-60400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-50800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-54200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-61700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-37200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-36000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-37700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-26300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-43300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-31900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-30800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-30000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-16900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-60100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-29100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-39500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-95300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-65800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-58500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-56700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-48600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-18700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-34400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-13100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-43500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-51400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-44900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-15900</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9483,8 +9707,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9599,124 +9826,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-52700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-49400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-53200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-310700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-54900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-65400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-42500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-47300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-36700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-47900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-43200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-126800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-53700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-108200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-66500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-102300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-29000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-69800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-38100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-103300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-18500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-113900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-63700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5681400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-26600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-550700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-512800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-283300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-235300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-91900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-57200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-363200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-22200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-49000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-24900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-340100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-290600</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9757,56 +9990,57 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>408400</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>402300</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>324300</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L96" s="3">
         <v>301500</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N96" s="3">
         <v>301500</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-243200</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -9814,11 +10048,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-155600</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -9826,11 +10060,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-199100</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -9838,11 +10072,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-198600</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -9850,11 +10084,11 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-41700</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
@@ -9862,19 +10096,22 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-57500</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
         <v>0</v>
       </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9989,8 +10226,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10105,8 +10345,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10221,352 +10464,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-52200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-317000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-150900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-118900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-518300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-147300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>14000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-349200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-242800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-349200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-781700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-708200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-964700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-615600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-525600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-501800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-240300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-88300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-455300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>18700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-311300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-118400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3968300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3203300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-178500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>5000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-317000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-206300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>22700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-79700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-34400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-99200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>9900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-79500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-4500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>156100</v>
+      </c>
+      <c r="E101" s="3">
         <v>22400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>35300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-69700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-47600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-158000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>94700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>27900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>94700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>27900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-50000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>111000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>125900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>27300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>64900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>30500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>31600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>45400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-76700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-43600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>31800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>72800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>11400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>27200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>24200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>49200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-34100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-75900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-63200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-143400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-7400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>41800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>896900</v>
+      </c>
+      <c r="E102" s="3">
         <v>253400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-186800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>313700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>305400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-69100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>569300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>221400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-134200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>24300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-134200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>759700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-429900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-399400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>193200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>31100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>65600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-267700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>814800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>598000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-250100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>110400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>496100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>325700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1340100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3384400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>333500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>103700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-276700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-329400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>641000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>378200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-347600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-30700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>373100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>385800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-175100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-209200</v>
       </c>
     </row>
